--- a/FROID_NR1_simulador.xlsx
+++ b/FROID_NR1_simulador.xlsx
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
